--- a/public/template/report_template.xlsx
+++ b/public/template/report_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\New folder (4)\A MY SYSTEM\TEST\IM BM TESTING\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DE\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C59E160-372C-4DC7-99A4-F9C1DC81EE44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFA720C-5437-4990-B5DD-99B3BAAB8A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D85457ED-C93B-4572-9923-33288398A231}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{D85457ED-C93B-4572-9923-33288398A231}"/>
   </bookViews>
   <sheets>
     <sheet name="28" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="49">
   <si>
     <t>Date   -</t>
   </si>
@@ -1054,445 +1054,448 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="40" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="39" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="52" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1812,1152 +1815,1179 @@
   <dimension ref="A1:AJ33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.1640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9.5" style="3" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="9.83203125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="7.83203125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.83203125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="8.1640625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="9.33203125" style="3"/>
-    <col min="12" max="36" width="4.1640625" style="3" customWidth="1"/>
-    <col min="37" max="79" width="5" style="3" customWidth="1"/>
-    <col min="80" max="16384" width="9.33203125" style="3"/>
+    <col min="1" max="1" width="17.1640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.5" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="7.83203125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.83203125" style="2" customWidth="1"/>
+    <col min="10" max="10" width="8.1640625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9.33203125" style="2"/>
+    <col min="12" max="36" width="4.1640625" style="2" customWidth="1"/>
+    <col min="37" max="79" width="5" style="2" customWidth="1"/>
+    <col min="80" max="16384" width="9.33203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
+      <c r="B1" s="143"/>
+      <c r="C1" s="143"/>
     </row>
     <row r="2" spans="1:36" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="144" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="Q2" s="5" t="s">
+      <c r="B2" s="144"/>
+      <c r="C2" s="144"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
+      <c r="Q2" s="145" t="s">
         <v>2</v>
       </c>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5"/>
-      <c r="AC2" s="5"/>
-      <c r="AD2" s="5"/>
-      <c r="AE2" s="5"/>
+      <c r="R2" s="145"/>
+      <c r="S2" s="145"/>
+      <c r="T2" s="145"/>
+      <c r="U2" s="145"/>
+      <c r="V2" s="145"/>
+      <c r="W2" s="145"/>
+      <c r="X2" s="145"/>
+      <c r="Y2" s="145"/>
+      <c r="Z2" s="145"/>
+      <c r="AA2" s="145"/>
+      <c r="AB2" s="145"/>
+      <c r="AC2" s="145"/>
+      <c r="AD2" s="145"/>
+      <c r="AE2" s="145"/>
     </row>
     <row r="3" spans="1:36" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
     </row>
     <row r="4" spans="1:36" ht="22.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="8" t="s">
+      <c r="C4" s="146"/>
+      <c r="D4" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="8" t="s">
+      <c r="E4" s="76"/>
+      <c r="F4" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="10"/>
-      <c r="H4" s="7" t="s">
+      <c r="G4" s="76"/>
+      <c r="H4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="11"/>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12"/>
-      <c r="O4" s="12" t="s">
+      <c r="L4" s="137"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="49"/>
+      <c r="O4" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="P4" s="12"/>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12" t="s">
+      <c r="P4" s="49"/>
+      <c r="Q4" s="49"/>
+      <c r="R4" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="12" t="s">
+      <c r="S4" s="49"/>
+      <c r="T4" s="49"/>
+      <c r="U4" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="V4" s="12"/>
-      <c r="W4" s="12"/>
-      <c r="Y4" s="11"/>
-      <c r="Z4" s="12"/>
-      <c r="AA4" s="12"/>
-      <c r="AB4" s="12" t="s">
+      <c r="V4" s="49"/>
+      <c r="W4" s="49"/>
+      <c r="Y4" s="137"/>
+      <c r="Z4" s="49"/>
+      <c r="AA4" s="49"/>
+      <c r="AB4" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="AC4" s="12"/>
-      <c r="AD4" s="12"/>
-      <c r="AE4" s="12" t="s">
+      <c r="AC4" s="49"/>
+      <c r="AD4" s="49"/>
+      <c r="AE4" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="AF4" s="12"/>
-      <c r="AG4" s="12"/>
-      <c r="AH4" s="12" t="s">
+      <c r="AF4" s="49"/>
+      <c r="AG4" s="49"/>
+      <c r="AH4" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="AI4" s="12"/>
-      <c r="AJ4" s="12"/>
+      <c r="AI4" s="49"/>
+      <c r="AJ4" s="49"/>
     </row>
     <row r="5" spans="1:36" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="18">
+      <c r="B5" s="138"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="140"/>
+      <c r="E5" s="139"/>
+      <c r="F5" s="140"/>
+      <c r="G5" s="141"/>
+      <c r="H5" s="6">
         <f>IFERROR(D5/B5,0)</f>
         <v>0</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="L5" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="21"/>
-      <c r="S5" s="19"/>
-      <c r="T5" s="20"/>
-      <c r="U5" s="22"/>
-      <c r="V5" s="23"/>
-      <c r="W5" s="23"/>
-      <c r="Y5" s="12" t="s">
+      <c r="M5" s="49"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="142"/>
+      <c r="P5" s="142"/>
+      <c r="Q5" s="103"/>
+      <c r="R5" s="98"/>
+      <c r="S5" s="142"/>
+      <c r="T5" s="103"/>
+      <c r="U5" s="64"/>
+      <c r="V5" s="135"/>
+      <c r="W5" s="135"/>
+      <c r="Y5" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="Z5" s="12"/>
-      <c r="AA5" s="12"/>
-      <c r="AB5" s="23"/>
-      <c r="AC5" s="23"/>
-      <c r="AD5" s="24"/>
-      <c r="AE5" s="25"/>
-      <c r="AF5" s="26"/>
-      <c r="AG5" s="27"/>
-      <c r="AH5" s="22"/>
-      <c r="AI5" s="23"/>
-      <c r="AJ5" s="23"/>
+      <c r="Z5" s="49"/>
+      <c r="AA5" s="49"/>
+      <c r="AB5" s="135"/>
+      <c r="AC5" s="135"/>
+      <c r="AD5" s="136"/>
+      <c r="AE5" s="133"/>
+      <c r="AF5" s="125"/>
+      <c r="AG5" s="129"/>
+      <c r="AH5" s="64"/>
+      <c r="AI5" s="135"/>
+      <c r="AJ5" s="135"/>
     </row>
     <row r="6" spans="1:36" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="18">
+      <c r="B6" s="88"/>
+      <c r="C6" s="117"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="89"/>
+      <c r="H6" s="6">
         <f t="shared" ref="H6:H15" si="0">IFERROR(D6/B6,0)</f>
         <v>0</v>
       </c>
-      <c r="L6" s="12" t="s">
+      <c r="L6" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="M6" s="12"/>
-      <c r="N6" s="12"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="33"/>
-      <c r="Q6" s="34"/>
-      <c r="R6" s="25"/>
-      <c r="S6" s="26"/>
-      <c r="T6" s="27"/>
-      <c r="U6" s="35"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="36"/>
-      <c r="X6" s="37"/>
-      <c r="Y6" s="12" t="s">
+      <c r="M6" s="49"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="119"/>
+      <c r="P6" s="119"/>
+      <c r="Q6" s="96"/>
+      <c r="R6" s="133"/>
+      <c r="S6" s="125"/>
+      <c r="T6" s="129"/>
+      <c r="U6" s="84"/>
+      <c r="V6" s="119"/>
+      <c r="W6" s="134"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="Z6" s="12"/>
-      <c r="AA6" s="38"/>
-      <c r="AB6" s="33"/>
-      <c r="AC6" s="33"/>
-      <c r="AD6" s="34"/>
-      <c r="AE6" s="35"/>
-      <c r="AF6" s="33"/>
-      <c r="AG6" s="34"/>
-      <c r="AH6" s="35"/>
-      <c r="AI6" s="33"/>
-      <c r="AJ6" s="33"/>
+      <c r="Z6" s="49"/>
+      <c r="AA6" s="94"/>
+      <c r="AB6" s="119"/>
+      <c r="AC6" s="119"/>
+      <c r="AD6" s="96"/>
+      <c r="AE6" s="84"/>
+      <c r="AF6" s="119"/>
+      <c r="AG6" s="96"/>
+      <c r="AH6" s="84"/>
+      <c r="AI6" s="119"/>
+      <c r="AJ6" s="119"/>
     </row>
     <row r="7" spans="1:36" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
+      <c r="A7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="32"/>
-      <c r="H7" s="18">
+      <c r="B7" s="88"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="88"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="89"/>
+      <c r="H7" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="L7" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="M7" s="12"/>
-      <c r="N7" s="12"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="41"/>
-      <c r="S7" s="42"/>
-      <c r="T7" s="43"/>
-      <c r="U7" s="35"/>
-      <c r="V7" s="33"/>
-      <c r="W7" s="33"/>
-      <c r="Y7" s="12" t="s">
+      <c r="M7" s="49"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="120"/>
+      <c r="P7" s="120"/>
+      <c r="Q7" s="65"/>
+      <c r="R7" s="130"/>
+      <c r="S7" s="131"/>
+      <c r="T7" s="132"/>
+      <c r="U7" s="84"/>
+      <c r="V7" s="119"/>
+      <c r="W7" s="119"/>
+      <c r="Y7" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="Z7" s="12"/>
-      <c r="AA7" s="38"/>
-      <c r="AB7" s="33"/>
-      <c r="AC7" s="33"/>
-      <c r="AD7" s="34"/>
-      <c r="AE7" s="25"/>
-      <c r="AF7" s="26"/>
-      <c r="AG7" s="27"/>
-      <c r="AH7" s="35"/>
-      <c r="AI7" s="33"/>
-      <c r="AJ7" s="33"/>
+      <c r="Z7" s="49"/>
+      <c r="AA7" s="94"/>
+      <c r="AB7" s="119"/>
+      <c r="AC7" s="119"/>
+      <c r="AD7" s="96"/>
+      <c r="AE7" s="133"/>
+      <c r="AF7" s="125"/>
+      <c r="AG7" s="129"/>
+      <c r="AH7" s="84"/>
+      <c r="AI7" s="119"/>
+      <c r="AJ7" s="119"/>
     </row>
     <row r="8" spans="1:36" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="30"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="30"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="45">
+      <c r="B8" s="88"/>
+      <c r="C8" s="117"/>
+      <c r="D8" s="88"/>
+      <c r="E8" s="117"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L8" s="12" t="s">
+      <c r="L8" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="35"/>
-      <c r="S8" s="33"/>
-      <c r="T8" s="34"/>
-      <c r="U8" s="25"/>
-      <c r="V8" s="26"/>
-      <c r="W8" s="26"/>
-      <c r="Y8" s="12" t="s">
+      <c r="M8" s="49"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="119"/>
+      <c r="P8" s="119"/>
+      <c r="Q8" s="96"/>
+      <c r="R8" s="84"/>
+      <c r="S8" s="119"/>
+      <c r="T8" s="96"/>
+      <c r="U8" s="133"/>
+      <c r="V8" s="125"/>
+      <c r="W8" s="125"/>
+      <c r="Y8" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="Z8" s="12"/>
-      <c r="AA8" s="38"/>
-      <c r="AB8" s="33"/>
-      <c r="AC8" s="33"/>
-      <c r="AD8" s="34"/>
-      <c r="AE8" s="35"/>
-      <c r="AF8" s="33"/>
-      <c r="AG8" s="34"/>
-      <c r="AH8" s="46"/>
-      <c r="AI8" s="39"/>
-      <c r="AJ8" s="39"/>
+      <c r="Z8" s="49"/>
+      <c r="AA8" s="94"/>
+      <c r="AB8" s="119"/>
+      <c r="AC8" s="119"/>
+      <c r="AD8" s="96"/>
+      <c r="AE8" s="84"/>
+      <c r="AF8" s="119"/>
+      <c r="AG8" s="96"/>
+      <c r="AH8" s="67"/>
+      <c r="AI8" s="120"/>
+      <c r="AJ8" s="120"/>
     </row>
     <row r="9" spans="1:36" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="51" t="s">
+      <c r="B9" s="126" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="127"/>
+      <c r="D9" s="126" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="128"/>
+      <c r="F9" s="126" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="128"/>
+      <c r="H9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="L9" s="12" t="s">
+      <c r="L9" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="27"/>
-      <c r="R9" s="41"/>
-      <c r="S9" s="42"/>
-      <c r="T9" s="43"/>
-      <c r="U9" s="35"/>
-      <c r="V9" s="33"/>
-      <c r="W9" s="33"/>
-      <c r="Y9" s="12" t="s">
+      <c r="M9" s="49"/>
+      <c r="N9" s="49"/>
+      <c r="O9" s="125"/>
+      <c r="P9" s="125"/>
+      <c r="Q9" s="129"/>
+      <c r="R9" s="130"/>
+      <c r="S9" s="131"/>
+      <c r="T9" s="132"/>
+      <c r="U9" s="84"/>
+      <c r="V9" s="119"/>
+      <c r="W9" s="119"/>
+      <c r="Y9" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="Z9" s="12"/>
-      <c r="AA9" s="12"/>
-      <c r="AB9" s="52"/>
-      <c r="AC9" s="33"/>
-      <c r="AD9" s="34"/>
-      <c r="AE9" s="46"/>
-      <c r="AF9" s="39"/>
-      <c r="AG9" s="40"/>
-      <c r="AH9" s="53"/>
-      <c r="AI9" s="26"/>
-      <c r="AJ9" s="26"/>
+      <c r="Z9" s="49"/>
+      <c r="AA9" s="49"/>
+      <c r="AB9" s="123"/>
+      <c r="AC9" s="119"/>
+      <c r="AD9" s="96"/>
+      <c r="AE9" s="67"/>
+      <c r="AF9" s="120"/>
+      <c r="AG9" s="65"/>
+      <c r="AH9" s="124"/>
+      <c r="AI9" s="125"/>
+      <c r="AJ9" s="125"/>
     </row>
     <row r="10" spans="1:36" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="54" t="s">
+      <c r="A10" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="18">
+      <c r="B10" s="88"/>
+      <c r="C10" s="117"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="117"/>
+      <c r="F10" s="118"/>
+      <c r="G10" s="89"/>
+      <c r="H10" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L10" s="12" t="s">
+      <c r="L10" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="12"/>
-      <c r="N10" s="12"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="34"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="34"/>
-      <c r="U10" s="46"/>
-      <c r="V10" s="39"/>
-      <c r="W10" s="39"/>
-      <c r="Y10" s="12" t="s">
+      <c r="M10" s="49"/>
+      <c r="N10" s="49"/>
+      <c r="O10" s="119"/>
+      <c r="P10" s="119"/>
+      <c r="Q10" s="96"/>
+      <c r="R10" s="84"/>
+      <c r="S10" s="119"/>
+      <c r="T10" s="96"/>
+      <c r="U10" s="67"/>
+      <c r="V10" s="120"/>
+      <c r="W10" s="120"/>
+      <c r="Y10" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="Z10" s="12"/>
-      <c r="AA10" s="12"/>
-      <c r="AB10" s="55"/>
-      <c r="AC10" s="39"/>
-      <c r="AD10" s="56"/>
-      <c r="AE10" s="46"/>
-      <c r="AF10" s="39"/>
-      <c r="AG10" s="40"/>
-      <c r="AH10" s="35"/>
-      <c r="AI10" s="33"/>
-      <c r="AJ10" s="33"/>
+      <c r="Z10" s="49"/>
+      <c r="AA10" s="49"/>
+      <c r="AB10" s="121"/>
+      <c r="AC10" s="120"/>
+      <c r="AD10" s="122"/>
+      <c r="AE10" s="67"/>
+      <c r="AF10" s="120"/>
+      <c r="AG10" s="65"/>
+      <c r="AH10" s="84"/>
+      <c r="AI10" s="119"/>
+      <c r="AJ10" s="119"/>
     </row>
     <row r="11" spans="1:36" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="18">
+      <c r="B11" s="88"/>
+      <c r="C11" s="117"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="117"/>
+      <c r="F11" s="118"/>
+      <c r="G11" s="89"/>
+      <c r="H11" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L11" s="12" t="s">
+      <c r="L11" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="M11" s="12"/>
-      <c r="N11" s="12"/>
-      <c r="O11" s="57"/>
-      <c r="P11" s="57"/>
-      <c r="Q11" s="58"/>
-      <c r="R11" s="59"/>
-      <c r="S11" s="57"/>
-      <c r="T11" s="58"/>
-      <c r="U11" s="60"/>
-      <c r="V11" s="61"/>
-      <c r="W11" s="61"/>
-      <c r="Y11" s="12" t="s">
+      <c r="M11" s="49"/>
+      <c r="N11" s="49"/>
+      <c r="O11" s="115"/>
+      <c r="P11" s="115"/>
+      <c r="Q11" s="95"/>
+      <c r="R11" s="78"/>
+      <c r="S11" s="115"/>
+      <c r="T11" s="95"/>
+      <c r="U11" s="112"/>
+      <c r="V11" s="113"/>
+      <c r="W11" s="113"/>
+      <c r="Y11" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="Z11" s="12"/>
-      <c r="AA11" s="12"/>
-      <c r="AB11" s="61"/>
-      <c r="AC11" s="61"/>
-      <c r="AD11" s="62"/>
-      <c r="AE11" s="59"/>
-      <c r="AF11" s="57"/>
-      <c r="AG11" s="58"/>
-      <c r="AH11" s="63"/>
-      <c r="AI11" s="61"/>
-      <c r="AJ11" s="61"/>
+      <c r="Z11" s="49"/>
+      <c r="AA11" s="49"/>
+      <c r="AB11" s="113"/>
+      <c r="AC11" s="113"/>
+      <c r="AD11" s="114"/>
+      <c r="AE11" s="78"/>
+      <c r="AF11" s="115"/>
+      <c r="AG11" s="95"/>
+      <c r="AH11" s="116"/>
+      <c r="AI11" s="113"/>
+      <c r="AJ11" s="113"/>
     </row>
     <row r="12" spans="1:36" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="30"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="30"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="18">
+      <c r="B12" s="88"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="88"/>
+      <c r="E12" s="117"/>
+      <c r="F12" s="88"/>
+      <c r="G12" s="89"/>
+      <c r="H12" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L12" s="12" t="s">
+      <c r="L12" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="M12" s="12"/>
-      <c r="N12" s="12"/>
-      <c r="O12" s="64"/>
-      <c r="P12" s="64"/>
-      <c r="Q12" s="64"/>
-      <c r="R12" s="64"/>
-      <c r="S12" s="64"/>
-      <c r="T12" s="64"/>
-      <c r="U12" s="64"/>
-      <c r="V12" s="64"/>
-      <c r="W12" s="64"/>
-      <c r="Y12" s="12" t="s">
+      <c r="M12" s="49"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="47"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="47"/>
+      <c r="T12" s="47"/>
+      <c r="U12" s="47"/>
+      <c r="V12" s="47"/>
+      <c r="W12" s="47"/>
+      <c r="Y12" s="49" t="s">
         <v>22</v>
       </c>
-      <c r="Z12" s="12"/>
-      <c r="AA12" s="12"/>
-      <c r="AB12" s="64"/>
-      <c r="AC12" s="64"/>
-      <c r="AD12" s="64"/>
-      <c r="AE12" s="64"/>
-      <c r="AF12" s="64"/>
-      <c r="AG12" s="64"/>
-      <c r="AH12" s="64"/>
-      <c r="AI12" s="64"/>
-      <c r="AJ12" s="64"/>
+      <c r="Z12" s="49"/>
+      <c r="AA12" s="49"/>
+      <c r="AB12" s="47"/>
+      <c r="AC12" s="47"/>
+      <c r="AD12" s="47"/>
+      <c r="AE12" s="47"/>
+      <c r="AF12" s="47"/>
+      <c r="AG12" s="47"/>
+      <c r="AH12" s="47"/>
+      <c r="AI12" s="47"/>
+      <c r="AJ12" s="47"/>
     </row>
     <row r="13" spans="1:36" ht="25.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="44" t="s">
+      <c r="A13" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="65"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="65"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="66"/>
-      <c r="H13" s="45">
+      <c r="B13" s="110"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="110"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L13" s="12" t="s">
+      <c r="L13" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12"/>
-      <c r="O13" s="64"/>
-      <c r="P13" s="64"/>
-      <c r="Q13" s="64"/>
-      <c r="R13" s="64"/>
-      <c r="S13" s="64"/>
-      <c r="T13" s="64"/>
-      <c r="U13" s="64"/>
-      <c r="V13" s="64"/>
-      <c r="W13" s="64"/>
-      <c r="Y13" s="12" t="s">
+      <c r="M13" s="49"/>
+      <c r="N13" s="49"/>
+      <c r="O13" s="47">
+        <f>O12-O11</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="47"/>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="47"/>
+      <c r="T13" s="47"/>
+      <c r="U13" s="47"/>
+      <c r="V13" s="47"/>
+      <c r="W13" s="47"/>
+      <c r="Y13" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="Z13" s="12"/>
-      <c r="AA13" s="12"/>
-      <c r="AB13" s="64"/>
-      <c r="AC13" s="64"/>
-      <c r="AD13" s="64"/>
-      <c r="AE13" s="64"/>
-      <c r="AF13" s="64"/>
-      <c r="AG13" s="64"/>
-      <c r="AH13" s="64"/>
-      <c r="AI13" s="64"/>
-      <c r="AJ13" s="64"/>
+      <c r="Z13" s="49"/>
+      <c r="AA13" s="49"/>
+      <c r="AB13" s="47">
+        <f>AB12-AB11</f>
+        <v>0</v>
+      </c>
+      <c r="AC13" s="47"/>
+      <c r="AD13" s="47"/>
+      <c r="AE13" s="47"/>
+      <c r="AF13" s="47"/>
+      <c r="AG13" s="47"/>
+      <c r="AH13" s="47"/>
+      <c r="AI13" s="47"/>
+      <c r="AJ13" s="47"/>
     </row>
     <row r="14" spans="1:36" ht="29.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="67" t="s">
+      <c r="A14" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="68"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="70">
+      <c r="B14" s="107"/>
+      <c r="C14" s="108"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="108"/>
+      <c r="F14" s="107"/>
+      <c r="G14" s="108"/>
+      <c r="H14" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:36" ht="28.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="67" t="s">
+      <c r="A15" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="68"/>
-      <c r="C15" s="71"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="71"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="71"/>
-      <c r="H15" s="72">
+      <c r="B15" s="107"/>
+      <c r="C15" s="109"/>
+      <c r="D15" s="107"/>
+      <c r="E15" s="109"/>
+      <c r="F15" s="107"/>
+      <c r="G15" s="109"/>
+      <c r="H15" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L15" s="73" t="s">
+      <c r="L15" s="104" t="s">
         <v>26</v>
       </c>
-      <c r="M15" s="73"/>
-      <c r="N15" s="73"/>
-      <c r="O15" s="73"/>
-      <c r="P15" s="73"/>
-      <c r="Q15" s="73"/>
-      <c r="R15" s="73"/>
-      <c r="S15" s="73"/>
-      <c r="T15" s="73"/>
-      <c r="U15" s="73"/>
-      <c r="V15" s="73"/>
-      <c r="W15" s="73"/>
-      <c r="X15" s="73"/>
-      <c r="Y15" s="73"/>
-      <c r="Z15" s="73"/>
-      <c r="AA15" s="73"/>
-      <c r="AB15" s="73"/>
-      <c r="AC15" s="73"/>
-      <c r="AD15" s="73"/>
-      <c r="AE15" s="73"/>
-      <c r="AF15" s="73"/>
-      <c r="AG15" s="73"/>
-      <c r="AH15" s="73"/>
-      <c r="AI15" s="73"/>
+      <c r="M15" s="104"/>
+      <c r="N15" s="104"/>
+      <c r="O15" s="104"/>
+      <c r="P15" s="104"/>
+      <c r="Q15" s="104"/>
+      <c r="R15" s="104"/>
+      <c r="S15" s="104"/>
+      <c r="T15" s="104"/>
+      <c r="U15" s="104"/>
+      <c r="V15" s="104"/>
+      <c r="W15" s="104"/>
+      <c r="X15" s="104"/>
+      <c r="Y15" s="104"/>
+      <c r="Z15" s="104"/>
+      <c r="AA15" s="104"/>
+      <c r="AB15" s="104"/>
+      <c r="AC15" s="104"/>
+      <c r="AD15" s="104"/>
+      <c r="AE15" s="104"/>
+      <c r="AF15" s="104"/>
+      <c r="AG15" s="104"/>
+      <c r="AH15" s="104"/>
+      <c r="AI15" s="104"/>
     </row>
     <row r="16" spans="1:36" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="L16" s="73"/>
-      <c r="M16" s="73"/>
-      <c r="N16" s="73"/>
-      <c r="O16" s="73"/>
-      <c r="P16" s="73"/>
-      <c r="Q16" s="73"/>
-      <c r="R16" s="73"/>
-      <c r="S16" s="73"/>
-      <c r="T16" s="73"/>
-      <c r="U16" s="73"/>
-      <c r="V16" s="73"/>
-      <c r="W16" s="73"/>
-      <c r="X16" s="73"/>
-      <c r="Y16" s="73"/>
-      <c r="Z16" s="73"/>
-      <c r="AA16" s="73"/>
-      <c r="AB16" s="73"/>
-      <c r="AC16" s="73"/>
-      <c r="AD16" s="73"/>
-      <c r="AE16" s="73"/>
-      <c r="AF16" s="73"/>
-      <c r="AG16" s="73"/>
-      <c r="AH16" s="73"/>
-      <c r="AI16" s="73"/>
+      <c r="L16" s="104"/>
+      <c r="M16" s="104"/>
+      <c r="N16" s="104"/>
+      <c r="O16" s="104"/>
+      <c r="P16" s="104"/>
+      <c r="Q16" s="104"/>
+      <c r="R16" s="104"/>
+      <c r="S16" s="104"/>
+      <c r="T16" s="104"/>
+      <c r="U16" s="104"/>
+      <c r="V16" s="104"/>
+      <c r="W16" s="104"/>
+      <c r="X16" s="104"/>
+      <c r="Y16" s="104"/>
+      <c r="Z16" s="104"/>
+      <c r="AA16" s="104"/>
+      <c r="AB16" s="104"/>
+      <c r="AC16" s="104"/>
+      <c r="AD16" s="104"/>
+      <c r="AE16" s="104"/>
+      <c r="AF16" s="104"/>
+      <c r="AG16" s="104"/>
+      <c r="AH16" s="104"/>
+      <c r="AI16" s="104"/>
     </row>
     <row r="17" spans="1:35" ht="30.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="L17" s="74"/>
-      <c r="M17" s="74"/>
-      <c r="N17" s="74"/>
-      <c r="O17" s="74"/>
-      <c r="P17" s="75" t="s">
+      <c r="L17" s="73"/>
+      <c r="M17" s="73"/>
+      <c r="N17" s="73"/>
+      <c r="O17" s="73"/>
+      <c r="P17" s="105" t="s">
         <v>27</v>
       </c>
-      <c r="Q17" s="75"/>
-      <c r="R17" s="75"/>
-      <c r="S17" s="76" t="s">
+      <c r="Q17" s="105"/>
+      <c r="R17" s="105"/>
+      <c r="S17" s="106" t="s">
         <v>28</v>
       </c>
-      <c r="T17" s="76"/>
-      <c r="U17" s="76"/>
-      <c r="V17" s="76" t="s">
+      <c r="T17" s="106"/>
+      <c r="U17" s="106"/>
+      <c r="V17" s="106" t="s">
         <v>29</v>
       </c>
-      <c r="W17" s="76"/>
-      <c r="X17" s="76"/>
-      <c r="Y17" s="76" t="s">
+      <c r="W17" s="106"/>
+      <c r="X17" s="106"/>
+      <c r="Y17" s="106" t="s">
         <v>30</v>
       </c>
-      <c r="Z17" s="76"/>
-      <c r="AA17" s="76"/>
-      <c r="AB17" s="76" t="s">
+      <c r="Z17" s="106"/>
+      <c r="AA17" s="106"/>
+      <c r="AB17" s="106" t="s">
         <v>31</v>
       </c>
-      <c r="AC17" s="76"/>
-      <c r="AD17" s="76"/>
-      <c r="AE17" s="76" t="s">
+      <c r="AC17" s="106"/>
+      <c r="AD17" s="106"/>
+      <c r="AE17" s="106" t="s">
         <v>32</v>
       </c>
-      <c r="AF17" s="76"/>
-      <c r="AG17" s="76"/>
-      <c r="AH17" s="77"/>
-      <c r="AI17" s="77"/>
+      <c r="AF17" s="106"/>
+      <c r="AG17" s="106"/>
+      <c r="AH17" s="19"/>
+      <c r="AI17" s="19"/>
     </row>
     <row r="18" spans="1:35" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="38" t="s">
+      <c r="B18" s="49"/>
+      <c r="C18" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="38" t="s">
+      <c r="D18" s="72"/>
+      <c r="E18" s="72"/>
+      <c r="F18" s="72"/>
+      <c r="G18" s="72"/>
+      <c r="H18" s="72"/>
+      <c r="I18" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="J18" s="79"/>
-      <c r="L18" s="12" t="s">
+      <c r="J18" s="71"/>
+      <c r="L18" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12" t="s">
+      <c r="M18" s="49"/>
+      <c r="N18" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="O18" s="38"/>
-      <c r="P18" s="20"/>
-      <c r="Q18" s="80"/>
-      <c r="R18" s="80"/>
-      <c r="S18" s="80"/>
-      <c r="T18" s="80"/>
-      <c r="U18" s="80"/>
-      <c r="V18" s="80"/>
-      <c r="W18" s="80"/>
-      <c r="X18" s="80"/>
-      <c r="Y18" s="80"/>
-      <c r="Z18" s="80"/>
-      <c r="AA18" s="80"/>
-      <c r="AB18" s="80"/>
-      <c r="AC18" s="80"/>
-      <c r="AD18" s="80"/>
-      <c r="AE18" s="80"/>
-      <c r="AF18" s="80"/>
-      <c r="AG18" s="21"/>
+      <c r="O18" s="94"/>
+      <c r="P18" s="103"/>
+      <c r="Q18" s="97"/>
+      <c r="R18" s="97"/>
+      <c r="S18" s="97"/>
+      <c r="T18" s="97"/>
+      <c r="U18" s="97"/>
+      <c r="V18" s="97"/>
+      <c r="W18" s="97"/>
+      <c r="X18" s="97"/>
+      <c r="Y18" s="97"/>
+      <c r="Z18" s="97"/>
+      <c r="AA18" s="97"/>
+      <c r="AB18" s="97"/>
+      <c r="AC18" s="97"/>
+      <c r="AD18" s="97"/>
+      <c r="AE18" s="97"/>
+      <c r="AF18" s="97"/>
+      <c r="AG18" s="98"/>
     </row>
     <row r="19" spans="1:35" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="81" t="s">
+      <c r="A19" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="81"/>
-      <c r="C19" s="82" t="s">
+      <c r="B19" s="85"/>
+      <c r="C19" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="83"/>
-      <c r="E19" s="84"/>
-      <c r="F19" s="84"/>
-      <c r="G19" s="84"/>
-      <c r="H19" s="85"/>
-      <c r="I19" s="86">
+      <c r="D19" s="100"/>
+      <c r="E19" s="101"/>
+      <c r="F19" s="101"/>
+      <c r="G19" s="101"/>
+      <c r="H19" s="102"/>
+      <c r="I19" s="90">
         <f>IFERROR(E20/E19,0)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="87"/>
-      <c r="L19" s="12" t="s">
+      <c r="J19" s="91"/>
+      <c r="L19" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12" t="s">
+      <c r="M19" s="49"/>
+      <c r="N19" s="49" t="s">
         <v>39</v>
       </c>
-      <c r="O19" s="38"/>
-      <c r="P19" s="34"/>
-      <c r="Q19" s="88"/>
-      <c r="R19" s="88"/>
-      <c r="S19" s="88"/>
-      <c r="T19" s="88"/>
-      <c r="U19" s="88"/>
-      <c r="V19" s="88"/>
-      <c r="W19" s="88"/>
-      <c r="X19" s="88"/>
-      <c r="Y19" s="88"/>
-      <c r="Z19" s="88"/>
-      <c r="AA19" s="88"/>
-      <c r="AB19" s="88"/>
-      <c r="AC19" s="88"/>
-      <c r="AD19" s="88"/>
-      <c r="AE19" s="88"/>
-      <c r="AF19" s="88"/>
-      <c r="AG19" s="35"/>
+      <c r="O19" s="94"/>
+      <c r="P19" s="96"/>
+      <c r="Q19" s="83"/>
+      <c r="R19" s="83"/>
+      <c r="S19" s="83"/>
+      <c r="T19" s="83"/>
+      <c r="U19" s="83"/>
+      <c r="V19" s="83"/>
+      <c r="W19" s="83"/>
+      <c r="X19" s="83"/>
+      <c r="Y19" s="83"/>
+      <c r="Z19" s="83"/>
+      <c r="AA19" s="83"/>
+      <c r="AB19" s="83"/>
+      <c r="AC19" s="83"/>
+      <c r="AD19" s="83"/>
+      <c r="AE19" s="83"/>
+      <c r="AF19" s="83"/>
+      <c r="AG19" s="84"/>
     </row>
     <row r="20" spans="1:35" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="81"/>
-      <c r="B20" s="81"/>
-      <c r="C20" s="89" t="s">
+      <c r="A20" s="85"/>
+      <c r="B20" s="85"/>
+      <c r="C20" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="90"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="92"/>
-      <c r="L20" s="12" t="s">
+      <c r="D20" s="87"/>
+      <c r="E20" s="88"/>
+      <c r="F20" s="88"/>
+      <c r="G20" s="88"/>
+      <c r="H20" s="89"/>
+      <c r="I20" s="92"/>
+      <c r="J20" s="93"/>
+      <c r="L20" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="M20" s="12"/>
-      <c r="N20" s="12" t="s">
+      <c r="M20" s="49"/>
+      <c r="N20" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="O20" s="38"/>
-      <c r="P20" s="34"/>
-      <c r="Q20" s="88"/>
-      <c r="R20" s="88"/>
-      <c r="S20" s="88"/>
-      <c r="T20" s="88"/>
-      <c r="U20" s="88"/>
-      <c r="V20" s="88"/>
-      <c r="W20" s="88"/>
-      <c r="X20" s="88"/>
-      <c r="Y20" s="88"/>
-      <c r="Z20" s="88"/>
-      <c r="AA20" s="88"/>
-      <c r="AB20" s="88"/>
-      <c r="AC20" s="88"/>
-      <c r="AD20" s="88"/>
-      <c r="AE20" s="88"/>
-      <c r="AF20" s="88"/>
-      <c r="AG20" s="35"/>
+      <c r="O20" s="94"/>
+      <c r="P20" s="96"/>
+      <c r="Q20" s="83"/>
+      <c r="R20" s="83"/>
+      <c r="S20" s="83"/>
+      <c r="T20" s="83"/>
+      <c r="U20" s="83"/>
+      <c r="V20" s="83"/>
+      <c r="W20" s="83"/>
+      <c r="X20" s="83"/>
+      <c r="Y20" s="83"/>
+      <c r="Z20" s="83"/>
+      <c r="AA20" s="83"/>
+      <c r="AB20" s="83"/>
+      <c r="AC20" s="83"/>
+      <c r="AD20" s="83"/>
+      <c r="AE20" s="83"/>
+      <c r="AF20" s="83"/>
+      <c r="AG20" s="84"/>
     </row>
     <row r="21" spans="1:35" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="81" t="s">
+      <c r="A21" s="85" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="81"/>
-      <c r="C21" s="89" t="s">
+      <c r="B21" s="85"/>
+      <c r="C21" s="86" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="90"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="86">
+      <c r="D21" s="87"/>
+      <c r="E21" s="88"/>
+      <c r="F21" s="88"/>
+      <c r="G21" s="88"/>
+      <c r="H21" s="89"/>
+      <c r="I21" s="90">
         <f>IFERROR(E22/E21,0)</f>
         <v>0</v>
       </c>
-      <c r="J21" s="87"/>
-      <c r="L21" s="12" t="s">
+      <c r="J21" s="91"/>
+      <c r="L21" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="M21" s="12"/>
-      <c r="N21" s="12" t="s">
+      <c r="M21" s="49"/>
+      <c r="N21" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="O21" s="38"/>
-      <c r="P21" s="58"/>
-      <c r="Q21" s="93"/>
-      <c r="R21" s="93"/>
-      <c r="S21" s="93"/>
-      <c r="T21" s="93"/>
-      <c r="U21" s="93"/>
-      <c r="V21" s="93"/>
-      <c r="W21" s="93"/>
-      <c r="X21" s="93"/>
-      <c r="Y21" s="93"/>
-      <c r="Z21" s="93"/>
-      <c r="AA21" s="93"/>
-      <c r="AB21" s="93"/>
-      <c r="AC21" s="93"/>
-      <c r="AD21" s="93"/>
-      <c r="AE21" s="93"/>
-      <c r="AF21" s="93"/>
-      <c r="AG21" s="59"/>
+      <c r="O21" s="94"/>
+      <c r="P21" s="95"/>
+      <c r="Q21" s="77"/>
+      <c r="R21" s="77"/>
+      <c r="S21" s="77"/>
+      <c r="T21" s="77"/>
+      <c r="U21" s="77"/>
+      <c r="V21" s="77"/>
+      <c r="W21" s="77"/>
+      <c r="X21" s="77"/>
+      <c r="Y21" s="77"/>
+      <c r="Z21" s="77"/>
+      <c r="AA21" s="77"/>
+      <c r="AB21" s="77"/>
+      <c r="AC21" s="77"/>
+      <c r="AD21" s="77"/>
+      <c r="AE21" s="77"/>
+      <c r="AF21" s="77"/>
+      <c r="AG21" s="78"/>
     </row>
     <row r="22" spans="1:35" ht="21" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="81"/>
-      <c r="B22" s="81"/>
-      <c r="C22" s="94" t="s">
+      <c r="A22" s="85"/>
+      <c r="B22" s="85"/>
+      <c r="C22" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="D22" s="95"/>
-      <c r="E22" s="96"/>
-      <c r="F22" s="96"/>
-      <c r="G22" s="96"/>
-      <c r="H22" s="97"/>
-      <c r="I22" s="91"/>
-      <c r="J22" s="92"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="82"/>
+      <c r="I22" s="92"/>
+      <c r="J22" s="93"/>
     </row>
     <row r="23" spans="1:35" ht="16.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="98"/>
-      <c r="B23" s="99"/>
-      <c r="C23" s="100"/>
-      <c r="D23" s="100"/>
-      <c r="E23" s="100"/>
-      <c r="F23" s="100"/>
-      <c r="G23" s="100"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
     </row>
     <row r="24" spans="1:35" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="101" t="s">
+      <c r="A24" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="101"/>
-      <c r="C24" s="101"/>
-      <c r="D24" s="101"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="101"/>
-      <c r="G24" s="101"/>
-      <c r="H24" s="101"/>
-      <c r="I24" s="101"/>
-      <c r="J24" s="101"/>
-      <c r="K24" s="101"/>
-      <c r="L24" s="102"/>
-      <c r="M24" s="102"/>
-      <c r="N24" s="102"/>
-      <c r="O24" s="102"/>
-      <c r="P24" s="103" t="s">
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="68"/>
+      <c r="G24" s="68"/>
+      <c r="H24" s="68"/>
+      <c r="I24" s="68"/>
+      <c r="J24" s="68"/>
+      <c r="K24" s="68"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="23"/>
+      <c r="O24" s="23"/>
+      <c r="P24" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="Q24" s="103"/>
-      <c r="R24" s="103"/>
-      <c r="S24" s="103"/>
-      <c r="T24" s="103"/>
-      <c r="U24" s="103"/>
-      <c r="V24" s="103"/>
-      <c r="W24" s="103"/>
-      <c r="X24" s="103"/>
-      <c r="Y24" s="103"/>
-      <c r="Z24" s="103"/>
-      <c r="AA24" s="103"/>
-      <c r="AB24" s="103"/>
-      <c r="AC24" s="103"/>
-      <c r="AD24" s="102"/>
-      <c r="AE24" s="102"/>
-      <c r="AF24" s="102"/>
+      <c r="Q24" s="69"/>
+      <c r="R24" s="69"/>
+      <c r="S24" s="69"/>
+      <c r="T24" s="69"/>
+      <c r="U24" s="69"/>
+      <c r="V24" s="69"/>
+      <c r="W24" s="69"/>
+      <c r="X24" s="69"/>
+      <c r="Y24" s="69"/>
+      <c r="Z24" s="69"/>
+      <c r="AA24" s="69"/>
+      <c r="AB24" s="69"/>
+      <c r="AC24" s="69"/>
+      <c r="AD24" s="23"/>
+      <c r="AE24" s="23"/>
+      <c r="AF24" s="23"/>
     </row>
     <row r="25" spans="1:35" ht="33.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="104" t="s">
+      <c r="A25" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="B25" s="79"/>
-      <c r="C25" s="78" t="s">
+      <c r="B25" s="71"/>
+      <c r="C25" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="D25" s="78"/>
-      <c r="E25" s="78"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="78"/>
-      <c r="H25" s="78"/>
-      <c r="I25" s="79"/>
-      <c r="J25" s="12" t="s">
+      <c r="D25" s="72"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="72"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="72"/>
+      <c r="I25" s="71"/>
+      <c r="J25" s="49" t="s">
         <v>46</v>
       </c>
-      <c r="K25" s="12"/>
-      <c r="L25" s="74"/>
-      <c r="M25" s="74"/>
-      <c r="N25" s="74"/>
-      <c r="O25" s="74"/>
-      <c r="P25" s="74"/>
-      <c r="Q25" s="74"/>
-      <c r="R25" s="74"/>
-      <c r="S25" s="8" t="s">
+      <c r="K25" s="49"/>
+      <c r="L25" s="73"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="73"/>
+      <c r="O25" s="73"/>
+      <c r="P25" s="73"/>
+      <c r="Q25" s="73"/>
+      <c r="R25" s="73"/>
+      <c r="S25" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="T25" s="105"/>
-      <c r="U25" s="105"/>
-      <c r="V25" s="105"/>
-      <c r="W25" s="105"/>
-      <c r="X25" s="105"/>
-      <c r="Y25" s="10"/>
-      <c r="Z25" s="8" t="s">
+      <c r="T25" s="75"/>
+      <c r="U25" s="75"/>
+      <c r="V25" s="75"/>
+      <c r="W25" s="75"/>
+      <c r="X25" s="75"/>
+      <c r="Y25" s="76"/>
+      <c r="Z25" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="AA25" s="105"/>
-      <c r="AB25" s="105"/>
-      <c r="AC25" s="105"/>
-      <c r="AD25" s="105"/>
-      <c r="AE25" s="105"/>
-      <c r="AF25" s="10"/>
+      <c r="AA25" s="75"/>
+      <c r="AB25" s="75"/>
+      <c r="AC25" s="75"/>
+      <c r="AD25" s="75"/>
+      <c r="AE25" s="75"/>
+      <c r="AF25" s="76"/>
     </row>
     <row r="26" spans="1:35" ht="22.5" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="106" t="s">
+      <c r="A26" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="107"/>
-      <c r="C26" s="108" t="s">
+      <c r="B26" s="44"/>
+      <c r="C26" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="D26" s="109"/>
-      <c r="E26" s="110"/>
-      <c r="F26" s="111"/>
-      <c r="G26" s="111"/>
-      <c r="H26" s="111"/>
-      <c r="I26" s="112"/>
-      <c r="J26" s="113"/>
-      <c r="K26" s="114"/>
-      <c r="L26" s="12" t="s">
+      <c r="D26" s="59"/>
+      <c r="E26" s="60"/>
+      <c r="F26" s="61"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="62"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="63">
+        <f>J26+J27</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="12"/>
-      <c r="P26" s="12"/>
-      <c r="Q26" s="12"/>
-      <c r="R26" s="12"/>
-      <c r="S26" s="40"/>
-      <c r="T26" s="115"/>
-      <c r="U26" s="115"/>
-      <c r="V26" s="115"/>
-      <c r="W26" s="115"/>
-      <c r="X26" s="115"/>
-      <c r="Y26" s="46"/>
-      <c r="Z26" s="116"/>
-      <c r="AA26" s="117"/>
-      <c r="AB26" s="117"/>
-      <c r="AC26" s="117"/>
-      <c r="AD26" s="117"/>
-      <c r="AE26" s="117"/>
-      <c r="AF26" s="118"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="49"/>
+      <c r="O26" s="49"/>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="49"/>
+      <c r="R26" s="49"/>
+      <c r="S26" s="65"/>
+      <c r="T26" s="66"/>
+      <c r="U26" s="66"/>
+      <c r="V26" s="66"/>
+      <c r="W26" s="66"/>
+      <c r="X26" s="66"/>
+      <c r="Y26" s="67"/>
+      <c r="Z26" s="51"/>
+      <c r="AA26" s="52"/>
+      <c r="AB26" s="52"/>
+      <c r="AC26" s="52"/>
+      <c r="AD26" s="52"/>
+      <c r="AE26" s="52"/>
+      <c r="AF26" s="53"/>
     </row>
     <row r="27" spans="1:35" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="119"/>
-      <c r="B27" s="120"/>
-      <c r="C27" s="121" t="s">
+      <c r="A27" s="45"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="D27" s="122"/>
-      <c r="E27" s="123"/>
-      <c r="F27" s="124"/>
-      <c r="G27" s="124"/>
-      <c r="H27" s="124"/>
-      <c r="I27" s="125"/>
-      <c r="J27" s="113"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="12" t="s">
+      <c r="D27" s="39"/>
+      <c r="E27" s="40"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="64"/>
+      <c r="L27" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="126"/>
-      <c r="T27" s="127"/>
-      <c r="U27" s="127"/>
-      <c r="V27" s="127"/>
-      <c r="W27" s="127"/>
-      <c r="X27" s="127"/>
-      <c r="Y27" s="128"/>
-      <c r="Z27" s="129"/>
-      <c r="AA27" s="127"/>
-      <c r="AB27" s="127"/>
-      <c r="AC27" s="127"/>
-      <c r="AD27" s="127"/>
-      <c r="AE27" s="127"/>
-      <c r="AF27" s="128"/>
+      <c r="M27" s="49"/>
+      <c r="N27" s="49"/>
+      <c r="O27" s="49"/>
+      <c r="P27" s="49"/>
+      <c r="Q27" s="49"/>
+      <c r="R27" s="49"/>
+      <c r="S27" s="54"/>
+      <c r="T27" s="55"/>
+      <c r="U27" s="55"/>
+      <c r="V27" s="55"/>
+      <c r="W27" s="55"/>
+      <c r="X27" s="55"/>
+      <c r="Y27" s="56"/>
+      <c r="Z27" s="57"/>
+      <c r="AA27" s="55"/>
+      <c r="AB27" s="55"/>
+      <c r="AC27" s="55"/>
+      <c r="AD27" s="55"/>
+      <c r="AE27" s="55"/>
+      <c r="AF27" s="56"/>
     </row>
     <row r="28" spans="1:35" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="106" t="s">
+      <c r="A28" s="43" t="s">
         <v>13</v>
       </c>
-      <c r="B28" s="107"/>
-      <c r="C28" s="121" t="s">
+      <c r="B28" s="44"/>
+      <c r="C28" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="D28" s="122"/>
-      <c r="E28" s="123"/>
-      <c r="F28" s="124"/>
-      <c r="G28" s="124"/>
-      <c r="H28" s="124"/>
-      <c r="I28" s="125"/>
-      <c r="J28" s="130"/>
-      <c r="K28" s="64"/>
-      <c r="L28" s="12" t="s">
+      <c r="D28" s="39"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="63">
+        <f t="shared" ref="K28" si="1">J28+J29</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="12"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
-      <c r="R28" s="12"/>
-      <c r="S28" s="131"/>
-      <c r="T28" s="132"/>
-      <c r="U28" s="132"/>
-      <c r="V28" s="132"/>
-      <c r="W28" s="132"/>
-      <c r="X28" s="132"/>
-      <c r="Y28" s="133"/>
-      <c r="Z28" s="134"/>
-      <c r="AA28" s="132"/>
-      <c r="AB28" s="132"/>
-      <c r="AC28" s="132"/>
-      <c r="AD28" s="132"/>
-      <c r="AE28" s="132"/>
-      <c r="AF28" s="133"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="49"/>
+      <c r="O28" s="49"/>
+      <c r="P28" s="49"/>
+      <c r="Q28" s="49"/>
+      <c r="R28" s="49"/>
+      <c r="S28" s="50">
+        <f>S27+S26</f>
+        <v>0</v>
+      </c>
+      <c r="T28" s="36"/>
+      <c r="U28" s="36"/>
+      <c r="V28" s="36"/>
+      <c r="W28" s="36"/>
+      <c r="X28" s="36"/>
+      <c r="Y28" s="37"/>
+      <c r="Z28" s="35">
+        <f>Z27+Z26</f>
+        <v>0</v>
+      </c>
+      <c r="AA28" s="36"/>
+      <c r="AB28" s="36"/>
+      <c r="AC28" s="36"/>
+      <c r="AD28" s="36"/>
+      <c r="AE28" s="36"/>
+      <c r="AF28" s="37"/>
     </row>
     <row r="29" spans="1:35" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="119"/>
-      <c r="B29" s="120"/>
-      <c r="C29" s="121" t="s">
+      <c r="A29" s="45"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="D29" s="122"/>
-      <c r="E29" s="123"/>
-      <c r="F29" s="124"/>
-      <c r="G29" s="124"/>
-      <c r="H29" s="124"/>
-      <c r="I29" s="125"/>
-      <c r="J29" s="113"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="40"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="15"/>
       <c r="K29" s="64"/>
     </row>
     <row r="30" spans="1:35" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="106" t="s">
+      <c r="A30" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="B30" s="107"/>
-      <c r="C30" s="121" t="s">
+      <c r="B30" s="44"/>
+      <c r="C30" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="122"/>
-      <c r="E30" s="123"/>
-      <c r="F30" s="124"/>
-      <c r="G30" s="124"/>
-      <c r="H30" s="124"/>
-      <c r="I30" s="125"/>
-      <c r="J30" s="113"/>
-      <c r="K30" s="64"/>
-      <c r="M30" s="135" t="s">
+      <c r="D30" s="39"/>
+      <c r="E30" s="40"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="41"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="147"/>
+      <c r="K30" s="47">
+        <f t="shared" ref="K30" si="2">J30+J31</f>
+        <v>0</v>
+      </c>
+      <c r="M30" s="48" t="s">
         <v>48</v>
       </c>
-      <c r="N30" s="135"/>
-      <c r="O30" s="135"/>
-      <c r="P30" s="135"/>
-      <c r="Q30" s="135"/>
-      <c r="R30" s="135"/>
-      <c r="S30" s="136"/>
-      <c r="T30" s="136"/>
-      <c r="U30" s="136"/>
-      <c r="V30" s="136"/>
-      <c r="W30" s="136"/>
-      <c r="X30" s="136"/>
-      <c r="Y30" s="136"/>
-      <c r="Z30" s="136"/>
-      <c r="AA30" s="136"/>
-      <c r="AB30" s="136"/>
-      <c r="AC30" s="136"/>
-      <c r="AD30" s="136"/>
+      <c r="N30" s="48"/>
+      <c r="O30" s="48"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="48"/>
+      <c r="R30" s="48"/>
+      <c r="S30" s="34"/>
+      <c r="T30" s="34"/>
+      <c r="U30" s="34"/>
+      <c r="V30" s="34"/>
+      <c r="W30" s="34"/>
+      <c r="X30" s="34"/>
+      <c r="Y30" s="34"/>
+      <c r="Z30" s="34"/>
+      <c r="AA30" s="34"/>
+      <c r="AB30" s="34"/>
+      <c r="AC30" s="34"/>
+      <c r="AD30" s="34"/>
     </row>
     <row r="31" spans="1:35" ht="20.25" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="119"/>
-      <c r="B31" s="120"/>
-      <c r="C31" s="137" t="s">
+      <c r="A31" s="45"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D31" s="138"/>
-      <c r="E31" s="139"/>
-      <c r="F31" s="140"/>
-      <c r="G31" s="140"/>
-      <c r="H31" s="140"/>
-      <c r="I31" s="141"/>
-      <c r="J31" s="142"/>
-      <c r="K31" s="64"/>
-      <c r="M31" s="143"/>
-      <c r="N31" s="143"/>
-      <c r="O31" s="143"/>
-      <c r="P31" s="143"/>
-      <c r="Q31" s="144"/>
-      <c r="R31" s="144"/>
-      <c r="S31" s="136"/>
-      <c r="T31" s="136"/>
-      <c r="U31" s="136"/>
-      <c r="V31" s="136"/>
-      <c r="W31" s="136"/>
-      <c r="X31" s="136"/>
-      <c r="Y31" s="136"/>
-      <c r="Z31" s="136"/>
-      <c r="AA31" s="136"/>
-      <c r="AB31" s="136"/>
-      <c r="AC31" s="136"/>
-      <c r="AD31" s="136"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="32"/>
+      <c r="G31" s="32"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="47"/>
+      <c r="M31" s="27"/>
+      <c r="N31" s="27"/>
+      <c r="O31" s="27"/>
+      <c r="P31" s="27"/>
+      <c r="Q31" s="25"/>
+      <c r="R31" s="25"/>
+      <c r="S31" s="34"/>
+      <c r="T31" s="34"/>
+      <c r="U31" s="34"/>
+      <c r="V31" s="34"/>
+      <c r="W31" s="34"/>
+      <c r="X31" s="34"/>
+      <c r="Y31" s="34"/>
+      <c r="Z31" s="34"/>
+      <c r="AA31" s="34"/>
+      <c r="AB31" s="34"/>
+      <c r="AC31" s="34"/>
+      <c r="AD31" s="34"/>
     </row>
     <row r="32" spans="1:35" ht="17.25" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="K32" s="145"/>
-      <c r="M32" s="143"/>
-      <c r="N32" s="143"/>
-      <c r="O32" s="143"/>
-      <c r="P32" s="143"/>
-      <c r="Q32" s="144"/>
-      <c r="R32" s="144"/>
-      <c r="S32" s="136"/>
-      <c r="T32" s="136"/>
-      <c r="U32" s="136"/>
-      <c r="V32" s="136"/>
-      <c r="W32" s="136"/>
-      <c r="X32" s="136"/>
-      <c r="Y32" s="136"/>
-      <c r="Z32" s="136"/>
-      <c r="AA32" s="136"/>
-      <c r="AB32" s="136"/>
-      <c r="AC32" s="136"/>
-      <c r="AD32" s="136"/>
+      <c r="K32" s="26"/>
+      <c r="M32" s="27"/>
+      <c r="N32" s="27"/>
+      <c r="O32" s="27"/>
+      <c r="P32" s="27"/>
+      <c r="Q32" s="25"/>
+      <c r="R32" s="25"/>
+      <c r="S32" s="34"/>
+      <c r="T32" s="34"/>
+      <c r="U32" s="34"/>
+      <c r="V32" s="34"/>
+      <c r="W32" s="34"/>
+      <c r="X32" s="34"/>
+      <c r="Y32" s="34"/>
+      <c r="Z32" s="34"/>
+      <c r="AA32" s="34"/>
+      <c r="AB32" s="34"/>
+      <c r="AC32" s="34"/>
+      <c r="AD32" s="34"/>
     </row>
     <row r="33" spans="13:23" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="M33" s="143"/>
-      <c r="N33" s="143"/>
-      <c r="O33" s="143"/>
-      <c r="P33" s="143"/>
-      <c r="Q33" s="144"/>
-      <c r="R33" s="144"/>
-      <c r="S33" s="146"/>
-      <c r="T33" s="146"/>
-      <c r="U33" s="146"/>
-      <c r="V33" s="146"/>
-      <c r="W33" s="146"/>
+      <c r="M33" s="27"/>
+      <c r="N33" s="27"/>
+      <c r="O33" s="27"/>
+      <c r="P33" s="27"/>
+      <c r="Q33" s="25"/>
+      <c r="R33" s="25"/>
+      <c r="S33" s="28"/>
+      <c r="T33" s="28"/>
+      <c r="U33" s="28"/>
+      <c r="V33" s="28"/>
+      <c r="W33" s="28"/>
     </row>
   </sheetData>
   <protectedRanges>
@@ -2965,16 +2995,188 @@
     <protectedRange sqref="M33:S33 U33:W33" name="Range1_2_1_1_1_1_1_1_1_1"/>
   </protectedRanges>
   <mergeCells count="208">
-    <mergeCell ref="M33:P33"/>
-    <mergeCell ref="S33:W33"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:I31"/>
-    <mergeCell ref="M31:P31"/>
-    <mergeCell ref="S31:X31"/>
-    <mergeCell ref="Y31:AD31"/>
-    <mergeCell ref="M32:P32"/>
-    <mergeCell ref="S32:X32"/>
-    <mergeCell ref="Y32:AD32"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="Q2:AE2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="R4:T4"/>
+    <mergeCell ref="U4:W4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="O6:Q6"/>
+    <mergeCell ref="Y4:AA4"/>
+    <mergeCell ref="AB4:AD4"/>
+    <mergeCell ref="AE4:AG4"/>
+    <mergeCell ref="AH4:AJ4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="O5:Q5"/>
+    <mergeCell ref="R5:T5"/>
+    <mergeCell ref="R6:T6"/>
+    <mergeCell ref="U6:W6"/>
+    <mergeCell ref="Y6:AA6"/>
+    <mergeCell ref="AB6:AD6"/>
+    <mergeCell ref="AE6:AG6"/>
+    <mergeCell ref="AH6:AJ6"/>
+    <mergeCell ref="U5:W5"/>
+    <mergeCell ref="Y5:AA5"/>
+    <mergeCell ref="AB5:AD5"/>
+    <mergeCell ref="AE5:AG5"/>
+    <mergeCell ref="AH5:AJ5"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="O8:Q8"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="O7:Q7"/>
+    <mergeCell ref="R8:T8"/>
+    <mergeCell ref="U8:W8"/>
+    <mergeCell ref="Y8:AA8"/>
+    <mergeCell ref="AB8:AD8"/>
+    <mergeCell ref="AE8:AG8"/>
+    <mergeCell ref="AH8:AJ8"/>
+    <mergeCell ref="U7:W7"/>
+    <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="AB7:AD7"/>
+    <mergeCell ref="AE7:AG7"/>
+    <mergeCell ref="AH7:AJ7"/>
+    <mergeCell ref="R7:T7"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="O10:Q10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="O9:Q9"/>
+    <mergeCell ref="R10:T10"/>
+    <mergeCell ref="U10:W10"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="AB10:AD10"/>
+    <mergeCell ref="AE10:AG10"/>
+    <mergeCell ref="AH10:AJ10"/>
+    <mergeCell ref="U9:W9"/>
+    <mergeCell ref="Y9:AA9"/>
+    <mergeCell ref="AB9:AD9"/>
+    <mergeCell ref="AE9:AG9"/>
+    <mergeCell ref="AH9:AJ9"/>
+    <mergeCell ref="R9:T9"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="Y11:AA11"/>
+    <mergeCell ref="AB11:AD11"/>
+    <mergeCell ref="AE11:AG11"/>
+    <mergeCell ref="AH11:AJ11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="O12:W12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="O11:Q11"/>
+    <mergeCell ref="R11:T11"/>
+    <mergeCell ref="Y12:AA12"/>
+    <mergeCell ref="AB12:AJ12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="O13:W13"/>
+    <mergeCell ref="Y13:AA13"/>
+    <mergeCell ref="AB13:AJ13"/>
+    <mergeCell ref="L15:AI16"/>
+    <mergeCell ref="L17:O17"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="S17:U17"/>
+    <mergeCell ref="V17:X17"/>
+    <mergeCell ref="Y17:AA17"/>
+    <mergeCell ref="AB17:AD17"/>
+    <mergeCell ref="AE17:AG17"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="V18:X18"/>
+    <mergeCell ref="Y18:AA18"/>
+    <mergeCell ref="AB18:AD18"/>
+    <mergeCell ref="AE18:AG18"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:J20"/>
+    <mergeCell ref="L19:O19"/>
+    <mergeCell ref="P19:R19"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="L18:O18"/>
+    <mergeCell ref="P18:R18"/>
+    <mergeCell ref="S18:U18"/>
+    <mergeCell ref="S19:U19"/>
+    <mergeCell ref="V19:X19"/>
+    <mergeCell ref="Y19:AA19"/>
+    <mergeCell ref="AB19:AD19"/>
+    <mergeCell ref="AE19:AG19"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="L20:O20"/>
+    <mergeCell ref="P20:R20"/>
+    <mergeCell ref="S20:U20"/>
+    <mergeCell ref="V20:X20"/>
+    <mergeCell ref="Y20:AA20"/>
+    <mergeCell ref="AB20:AD20"/>
+    <mergeCell ref="AE20:AG20"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:H21"/>
+    <mergeCell ref="I21:J22"/>
+    <mergeCell ref="L21:O21"/>
+    <mergeCell ref="P21:R21"/>
+    <mergeCell ref="A24:K24"/>
+    <mergeCell ref="P24:AC24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="L25:R25"/>
+    <mergeCell ref="S25:Y25"/>
+    <mergeCell ref="Z25:AF25"/>
+    <mergeCell ref="S21:U21"/>
+    <mergeCell ref="V21:X21"/>
+    <mergeCell ref="Y21:AA21"/>
+    <mergeCell ref="AB21:AD21"/>
+    <mergeCell ref="AE21:AG21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:H22"/>
+    <mergeCell ref="Z26:AF26"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:I27"/>
+    <mergeCell ref="L27:R27"/>
+    <mergeCell ref="S27:Y27"/>
+    <mergeCell ref="Z27:AF27"/>
+    <mergeCell ref="A26:B27"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:I26"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="L26:R26"/>
+    <mergeCell ref="S26:Y26"/>
     <mergeCell ref="Z28:AF28"/>
     <mergeCell ref="C29:D29"/>
     <mergeCell ref="E29:I29"/>
@@ -2991,188 +3193,16 @@
     <mergeCell ref="K28:K29"/>
     <mergeCell ref="L28:R28"/>
     <mergeCell ref="S28:Y28"/>
-    <mergeCell ref="Z26:AF26"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:I27"/>
-    <mergeCell ref="L27:R27"/>
-    <mergeCell ref="S27:Y27"/>
-    <mergeCell ref="Z27:AF27"/>
-    <mergeCell ref="A26:B27"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:I26"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="L26:R26"/>
-    <mergeCell ref="S26:Y26"/>
-    <mergeCell ref="A24:K24"/>
-    <mergeCell ref="P24:AC24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="L25:R25"/>
-    <mergeCell ref="S25:Y25"/>
-    <mergeCell ref="Z25:AF25"/>
-    <mergeCell ref="S21:U21"/>
-    <mergeCell ref="V21:X21"/>
-    <mergeCell ref="Y21:AA21"/>
-    <mergeCell ref="AB21:AD21"/>
-    <mergeCell ref="AE21:AG21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:H22"/>
-    <mergeCell ref="V20:X20"/>
-    <mergeCell ref="Y20:AA20"/>
-    <mergeCell ref="AB20:AD20"/>
-    <mergeCell ref="AE20:AG20"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:H21"/>
-    <mergeCell ref="I21:J22"/>
-    <mergeCell ref="L21:O21"/>
-    <mergeCell ref="P21:R21"/>
-    <mergeCell ref="S19:U19"/>
-    <mergeCell ref="V19:X19"/>
-    <mergeCell ref="Y19:AA19"/>
-    <mergeCell ref="AB19:AD19"/>
-    <mergeCell ref="AE19:AG19"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="L20:O20"/>
-    <mergeCell ref="P20:R20"/>
-    <mergeCell ref="S20:U20"/>
-    <mergeCell ref="V18:X18"/>
-    <mergeCell ref="Y18:AA18"/>
-    <mergeCell ref="AB18:AD18"/>
-    <mergeCell ref="AE18:AG18"/>
-    <mergeCell ref="A19:B20"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:J20"/>
-    <mergeCell ref="L19:O19"/>
-    <mergeCell ref="P19:R19"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="L18:O18"/>
-    <mergeCell ref="P18:R18"/>
-    <mergeCell ref="S18:U18"/>
-    <mergeCell ref="L15:AI16"/>
-    <mergeCell ref="L17:O17"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="S17:U17"/>
-    <mergeCell ref="V17:X17"/>
-    <mergeCell ref="Y17:AA17"/>
-    <mergeCell ref="AB17:AD17"/>
-    <mergeCell ref="AE17:AG17"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="Y12:AA12"/>
-    <mergeCell ref="AB12:AJ12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="O13:W13"/>
-    <mergeCell ref="Y13:AA13"/>
-    <mergeCell ref="AB13:AJ13"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="Y11:AA11"/>
-    <mergeCell ref="AB11:AD11"/>
-    <mergeCell ref="AE11:AG11"/>
-    <mergeCell ref="AH11:AJ11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="O12:W12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="O11:Q11"/>
-    <mergeCell ref="R11:T11"/>
-    <mergeCell ref="R10:T10"/>
-    <mergeCell ref="U10:W10"/>
-    <mergeCell ref="Y10:AA10"/>
-    <mergeCell ref="AB10:AD10"/>
-    <mergeCell ref="AE10:AG10"/>
-    <mergeCell ref="AH10:AJ10"/>
-    <mergeCell ref="U9:W9"/>
-    <mergeCell ref="Y9:AA9"/>
-    <mergeCell ref="AB9:AD9"/>
-    <mergeCell ref="AE9:AG9"/>
-    <mergeCell ref="AH9:AJ9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="O10:Q10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="O9:Q9"/>
-    <mergeCell ref="R9:T9"/>
-    <mergeCell ref="R8:T8"/>
-    <mergeCell ref="U8:W8"/>
-    <mergeCell ref="Y8:AA8"/>
-    <mergeCell ref="AB8:AD8"/>
-    <mergeCell ref="AE8:AG8"/>
-    <mergeCell ref="AH8:AJ8"/>
-    <mergeCell ref="U7:W7"/>
-    <mergeCell ref="Y7:AA7"/>
-    <mergeCell ref="AB7:AD7"/>
-    <mergeCell ref="AE7:AG7"/>
-    <mergeCell ref="AH7:AJ7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="O8:Q8"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="O7:Q7"/>
-    <mergeCell ref="R7:T7"/>
-    <mergeCell ref="R6:T6"/>
-    <mergeCell ref="U6:W6"/>
-    <mergeCell ref="Y6:AA6"/>
-    <mergeCell ref="AB6:AD6"/>
-    <mergeCell ref="AE6:AG6"/>
-    <mergeCell ref="AH6:AJ6"/>
-    <mergeCell ref="U5:W5"/>
-    <mergeCell ref="Y5:AA5"/>
-    <mergeCell ref="AB5:AD5"/>
-    <mergeCell ref="AE5:AG5"/>
-    <mergeCell ref="AH5:AJ5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="O6:Q6"/>
-    <mergeCell ref="Y4:AA4"/>
-    <mergeCell ref="AB4:AD4"/>
-    <mergeCell ref="AE4:AG4"/>
-    <mergeCell ref="AH4:AJ4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="O5:Q5"/>
-    <mergeCell ref="R5:T5"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="Q2:AE2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="O4:Q4"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="U4:W4"/>
+    <mergeCell ref="M33:P33"/>
+    <mergeCell ref="S33:W33"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:I31"/>
+    <mergeCell ref="M31:P31"/>
+    <mergeCell ref="S31:X31"/>
+    <mergeCell ref="Y31:AD31"/>
+    <mergeCell ref="M32:P32"/>
+    <mergeCell ref="S32:X32"/>
+    <mergeCell ref="Y32:AD32"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.5" right="0" top="0.5" bottom="0.5" header="0" footer="0"/>
